--- a/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 Dr. Smith입니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 현장에서 정말 긴 하루를 보내고 나서, 아니면 동네 모임 다녀와서 집에 오면, 계획했던 것보다 훨씬 많이 먹는 때가 있어요. 남은 배달 음식이나 시리얼, 과자 같은 거, 뭐든 있는 대로요, 배가 불편할 정도로 부를 때까지요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그렇게 많이 드신 후에, 만회하려고 하시는 게 있나요? 예를 들어 일부러 토를 하거나, 완하제를 쓰거나, 금식을 하거나, 운동을 많이 하는 것처럼요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 달에 몇 번은, 그런 밤이 지나고 나면 화장실에 가서 일부러 토를 해요. 당황스럽고 꼭 되돌려야 할 것 같은 기분이 들어요, 특히 제가 단정해 보이려고 그렇게 애쓰는 걸 생각하면요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 석 달 동안, 이런 폭식-구토가 얼마나 자주 있었던 것 같으세요? 평균적으로 적어도 일주일에 한 번 정도였나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네... 돌이켜보면 평균적으로 일주일에 한 번 정도인 것 같아요. 어떤 주는 두 번, 또 어떤 주는 전혀 없기도 한데, 전체적으로 보면 대략 매주요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지금 키와 몸무게가 어떻게 되시는지, 아니면 대략적인 BMI를 알고 계시면 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 제 BMI는 잘 모르겠어요. 최근에 몸무게를 재본 적이 없어서 정확한 숫자는 말씀드리기 어려울 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지금 체중이 키에 비해 일반적으로 건강한 범위에 있는지, 그보다 많은지 적은지 알고 계신가요? 본인이든 의사든 체중이 심각하게 저체중이라고 말한 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 의사 선생님이 저체중이 심하다고 한 적은 없어요, 적어도 제가 기억하기로는요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 본인의 자존감이나 스스로에 대한 감정이 체형이나 체중에 많이 좌우된다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 몸에 맞는 작업복을 입기 시작하고 회의에서 앞에 나서게 되면서부터, 하루 전체를 바지가 꽉 끼는지, 사람들이 제 배를 볼 수 있을 것 같은지로 판단하고 있는 저 자신을 발견해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 폭식증 (D022)
 인구통계: 성별 여성 / 나이 34 / 직업상태 first line supervisor of construction trades or extraction worker / 최종학력 학사
@@ -575,212 +705,38 @@
 증상 지속 기간: 7 months
 추가 요건: The binge eating and inappropriate compensatory behaviors both occur, on average, at least once a week for 3 months
 주호소 증상 코드: S049
-배경 서술: Dianne의 증상은 그가 더 눈에 띄는 관리자 역할을 맡으면서 자신의 겉모습을 의도적으로 바꾸기 시작한 후 나타났다. 헐렁한 작업복 대신 더 몸에 맞는 정장 스타일의 옷을 입기 시작했고, 현장이나 시민 회의, 역사보존 행사에서 자신이 어떻게 보이는지에 더 신경을 쓰게 되었다. 7개월에 걸쳐 그의 승부욕과 대외적인 책임감 때문에 체형이 지나치게 중요하게 느껴지기 시작했고, 긴 근무일이나 동네 모임 후에 계획했던 것보다 훨씬 많이 먹는 일이 가끔 일어나면서 멈추기 어렵게 느껴지기 시작했다. 그는 이런 일을 되돌리기 위해 구토를 하기 시작했는데, 처음에는 여전히 일이나 지역사회 활동을 잘 해내고 있었기 때문에 이를 임상적 문제라기보다 개인적인 일탈로 여겼다. 그는 건설 회사의 건강 복지 프로그램과 연계된 직원 웰니스 상담 중 스스로 이 문제를 꺼내며, 패턴이 더 굳어지기 전에 도움을 요청하면서 정신건강의학과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 Dr. Smith입니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 현장에서 정말 긴 하루를 보내고 나서, 아니면 동네 모임 다녀와서 집에 오면, 계획했던 것보다 훨씬 많이 먹는 때가 있어요. 남은 배달 음식이나 시리얼, 과자 같은 거, 뭐든 있는 대로요, 배가 불편할 정도로 부를 때까지요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그렇게 많이 드신 후에, 만회하려고 하시는 게 있나요? 예를 들어 일부러 토를 하거나, 완하제를 쓰거나, 금식을 하거나, 운동을 많이 하는 것처럼요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 달에 몇 번은, 그런 밤이 지나고 나면 화장실에 가서 일부러 토를 해요. 당황스럽고 꼭 되돌려야 할 것 같은 기분이 들어요, 특히 제가 단정해 보이려고 그렇게 애쓰는 걸 생각하면요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 석 달 동안, 이런 폭식-구토가 얼마나 자주 있었던 것 같으세요? 평균적으로 적어도 일주일에 한 번 정도였나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네... 돌이켜보면 평균적으로 일주일에 한 번 정도인 것 같아요. 어떤 주는 두 번, 또 어떤 주는 전혀 없기도 한데, 전체적으로 보면 대략 매주요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지금 키와 몸무게가 어떻게 되시는지, 아니면 대략적인 BMI를 알고 계시면 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 제 BMI는 잘 모르겠어요. 최근에 몸무게를 재본 적이 없어서 정확한 숫자는 말씀드리기 어려울 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지금 체중이 키에 비해 일반적으로 건강한 범위에 있는지, 그보다 많은지 적은지 알고 계신가요? 본인이든 의사든 체중이 심각하게 저체중이라고 말한 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 의사 선생님이 저체중이 심하다고 한 적은 없어요, 적어도 제가 기억하기로는요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 본인의 자존감이나 스스로에 대한 감정이 체형이나 체중에 많이 좌우된다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 몸에 맞는 작업복을 입기 시작하고 회의에서 앞에 나서게 되면서부터, 하루 전체를 바지가 꽉 끼는지, 사람들이 제 배를 볼 수 있을 것 같은지로 판단하고 있는 저 자신을 발견해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: Dianne의 증상은 그가 더 눈에 띄는 관리자 역할을 맡으면서 자신의 겉모습을 의도적으로 바꾸기 시작한 후 나타났다. 헐렁한 작업복 대신 더 몸에 맞는 정장 스타일의 옷을 입기 시작했고, 현장이나 시민 회의, 역사보존 행사에서 자신이 어떻게 보이는지에 더 신경을 쓰게 되었다. 7개월에 걸쳐 그의 승부욕과 대외적인 책임감 때문에 체형이 지나치게 중요하게 느껴지기 시작했고, 긴 근무일이나 동네 모임 후에 계획했던 것보다 훨씬 많이 먹는 일이 가끔 일어나면서 멈추기 어렵게 느껴지기 시작했다. 그는 이런 일을 되돌리기 위해 구토를 하기 시작했는데, 처음에는 여전히 일이나 지역사회 활동을 잘 해내고 있었기 때문에 이를 임상적 문제라기보다 개인적인 일탈로 여겼다. 그는 건설 회사의 건강 복지 프로그램과 연계된 직원 웰니스 상담 중 스스로 이 문제를 꺼내며, 패턴이 더 굳어지기 전에 도움을 요청하면서 정신건강의학과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S048 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
-  누락: 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
-  누락: 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
-  누락: 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.</t>
+          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 있음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -732,11 +737,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S004_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.8889</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
